--- a/data/trans_dic/MCS12_SP_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,16; 45,45</t>
+          <t>36,31; 45,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,79; 55,81</t>
+          <t>45,44; 55,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,9; 52,29</t>
+          <t>42,31; 52,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,09; 46,16</t>
+          <t>36,86; 46,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,3; 56,5</t>
+          <t>45,65; 56,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,22; 62,08</t>
+          <t>50,03; 62,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,92; 54,24</t>
+          <t>42,64; 53,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,72; 48,58</t>
+          <t>40,18; 48,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,99; 48,32</t>
+          <t>40,96; 48,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,27; 56,84</t>
+          <t>49,61; 57,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,41; 51,59</t>
+          <t>44,5; 51,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,08; 46,05</t>
+          <t>40,17; 46,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,7; 44,04</t>
+          <t>34,06; 44,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,33; 53,54</t>
+          <t>43,08; 53,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,03; 51,9</t>
+          <t>41,19; 51,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,98; 41,27</t>
+          <t>31,93; 41,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,69; 60,23</t>
+          <t>50,09; 60,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,17; 69,81</t>
+          <t>58,55; 69,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,99; 58,15</t>
+          <t>47,83; 58,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,97; 53,58</t>
+          <t>45,26; 53,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,08; 50,53</t>
+          <t>43,3; 50,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,87; 59,78</t>
+          <t>51,54; 59,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,32; 53,55</t>
+          <t>46,14; 53,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,06; 45,67</t>
+          <t>39,3; 45,74</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,18; 48,91</t>
+          <t>40,77; 48,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,25; 57,31</t>
+          <t>48,67; 57,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,41; 55,44</t>
+          <t>46,59; 54,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 45,97</t>
+          <t>10,23; 46,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,07; 64,94</t>
+          <t>49,69; 64,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,77; 71,89</t>
+          <t>59,71; 71,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,09; 68,6</t>
+          <t>51,45; 68,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,01; 60,03</t>
+          <t>48,28; 60,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,93; 51,36</t>
+          <t>44,25; 51,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,32; 60,4</t>
+          <t>53,23; 60,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48,98; 56,75</t>
+          <t>49,06; 56,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 48,85</t>
+          <t>16,2; 48,55</t>
         </is>
       </c>
     </row>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,33; 50,96</t>
+          <t>45,29; 50,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,97; 54,51</t>
+          <t>48,25; 54,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,62; 53,56</t>
+          <t>47,28; 53,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,42; 46,06</t>
+          <t>39,57; 46,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,36; 57,35</t>
+          <t>49,57; 57,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,7; 65,08</t>
+          <t>56,78; 64,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,82; 58,69</t>
+          <t>51,96; 58,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,59; 79,01</t>
+          <t>47,85; 79,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,68; 57,39</t>
+          <t>52,96; 57,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,03; 54,86</t>
+          <t>50,51; 54,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,58; 66,38</t>
+          <t>44,52; 66,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,89; 48,66</t>
+          <t>37,35; 48,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,82; 51,1</t>
+          <t>42,09; 51,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,15; 54,73</t>
+          <t>46,57; 54,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,93; 50,58</t>
+          <t>41,34; 51,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,19; 62,67</t>
+          <t>54,24; 62,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,19; 68,5</t>
+          <t>61,19; 68,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,39; 66,73</t>
+          <t>59,1; 66,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,92; 66,6</t>
+          <t>50,12; 67,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,44; 55,91</t>
+          <t>49,17; 55,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,64; 60,2</t>
+          <t>54,84; 60,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,45; 60,16</t>
+          <t>54,43; 60,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,37; 60,32</t>
+          <t>48,52; 60,84</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,13; 33,8</t>
+          <t>23,64; 34,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,65; 37,8</t>
+          <t>26,67; 38,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,92; 38,07</t>
+          <t>27,28; 37,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,76; 37,55</t>
+          <t>18,85; 39,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,8; 55,59</t>
+          <t>50,09; 55,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57,48; 63,45</t>
+          <t>57,36; 63,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,95; 54,03</t>
+          <t>47,84; 53,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,59; 54,66</t>
+          <t>47,68; 54,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,57; 50,66</t>
+          <t>45,76; 50,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52,16; 57,68</t>
+          <t>52,22; 57,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44,25; 49,88</t>
+          <t>43,91; 49,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,73; 48,64</t>
+          <t>40,97; 48,33</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,56; 45,0</t>
+          <t>41,54; 44,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,25; 50,72</t>
+          <t>47,46; 50,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,43; 49,88</t>
+          <t>46,37; 49,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,37; 41,93</t>
+          <t>29,17; 41,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,47; 55,92</t>
+          <t>52,46; 55,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,31; 63,68</t>
+          <t>60,15; 63,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,24; 56,65</t>
+          <t>53,21; 56,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49,99; 62,92</t>
+          <t>49,86; 62,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,54; 50,01</t>
+          <t>47,69; 50,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54,3; 56,68</t>
+          <t>54,25; 56,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50,38; 52,87</t>
+          <t>50,44; 52,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,36; 50,82</t>
+          <t>41,45; 50,78</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>171310; 215330</t>
+          <t>172020; 215718</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>200213; 244018</t>
+          <t>198660; 243520</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>184085; 224386</t>
+          <t>181553; 225817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>186601; 232201</t>
+          <t>185402; 231597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>138923; 173276</t>
+          <t>139992; 172871</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>157930; 195224</t>
+          <t>157319; 195472</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>148968; 188226</t>
+          <t>147978; 186190</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>181661; 216774</t>
+          <t>179289; 215093</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>319913; 377087</t>
+          <t>319666; 376275</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>370318; 427265</t>
+          <t>372897; 430433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>344721; 400407</t>
+          <t>345409; 401286</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>380470; 437140</t>
+          <t>381295; 439304</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>123654; 161599</t>
+          <t>124975; 162708</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181450; 224232</t>
+          <t>180398; 223522</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154791; 195775</t>
+          <t>155381; 193907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144402; 186321</t>
+          <t>144150; 185933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>184767; 223974</t>
+          <t>186274; 225216</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>196610; 235975</t>
+          <t>197902; 235750</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>178646; 216477</t>
+          <t>178043; 217626</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>171783; 204691</t>
+          <t>172879; 205054</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>318256; 373322</t>
+          <t>319936; 375873</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>392570; 452409</t>
+          <t>390032; 447447</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>347145; 401320</t>
+          <t>345815; 401136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>325532; 380677</t>
+          <t>327589; 381267</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>217942; 265284</t>
+          <t>221154; 264703</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>310012; 360700</t>
+          <t>306322; 359513</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>242207; 289357</t>
+          <t>243169; 286879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65185; 305882</t>
+          <t>68038; 308981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82337; 108954</t>
+          <t>83374; 108198</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>155478; 186996</t>
+          <t>155336; 186897</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86533; 113958</t>
+          <t>85467; 113290</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79660; 99601</t>
+          <t>80101; 99694</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>311962; 364732</t>
+          <t>314274; 363911</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>474348; 537268</t>
+          <t>473510; 536656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>336980; 390468</t>
+          <t>337578; 392133</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>117024; 406123</t>
+          <t>134658; 403570</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>561358; 631030</t>
+          <t>560805; 629229</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>555998; 631817</t>
+          <t>559184; 631598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>547447; 615804</t>
+          <t>543590; 611526</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>405900; 474272</t>
+          <t>407484; 478087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>352558; 409617</t>
+          <t>354041; 411050</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>442370; 498940</t>
+          <t>435318; 493694</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>427983; 484688</t>
+          <t>429104; 485015</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>464353; 770952</t>
+          <t>466903; 771325</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>937319; 1026069</t>
+          <t>937270; 1026198</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1014420; 1105230</t>
+          <t>1019743; 1108702</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>988295; 1083743</t>
+          <t>997886; 1082847</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>893995; 1331290</t>
+          <t>892954; 1339211</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>132811; 170576</t>
+          <t>130915; 170269</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>213549; 260915</t>
+          <t>214914; 261379</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>286452; 339711</t>
+          <t>289039; 337445</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>192565; 237965</t>
+          <t>194466; 240959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>308230; 356458</t>
+          <t>308518; 357102</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>465941; 521622</t>
+          <t>465943; 517920</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>438434; 492621</t>
+          <t>436271; 493282</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>417650; 557175</t>
+          <t>419337; 562873</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>454541; 513940</t>
+          <t>452046; 512003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>695142; 765832</t>
+          <t>697606; 768597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739884; 817551</t>
+          <t>739682; 816384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>632197; 788387</t>
+          <t>634166; 795200</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>68976; 100791</t>
+          <t>70506; 101439</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71137; 100870</t>
+          <t>71178; 102671</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77301; 109325</t>
+          <t>78328; 108623</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42707; 90311</t>
+          <t>45343; 94102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>621916; 694243</t>
+          <t>625518; 694322</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>637654; 703925</t>
+          <t>636342; 702602</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>518861; 584664</t>
+          <t>517638; 583792</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>358162; 411380</t>
+          <t>358848; 409917</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>704927; 783761</t>
+          <t>707950; 783959</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>717904; 793777</t>
+          <t>718721; 794843</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>605902; 682960</t>
+          <t>601245; 681603</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>414384; 483058</t>
+          <t>406841; 480013</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1359187; 1471585</t>
+          <t>1358481; 1471031</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1616859; 1735751</t>
+          <t>1624206; 1738806</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1571990; 1688811</t>
+          <t>1570094; 1691389</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>986894; 1409180</t>
+          <t>980323; 1405243</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1772605; 1889024</t>
+          <t>1772265; 1889033</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2140915; 2260604</t>
+          <t>2135351; 2257824</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1880280; 2000762</t>
+          <t>1879204; 2002031</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1779209; 2239311</t>
+          <t>1774767; 2234950</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3160800; 3325063</t>
+          <t>3170890; 3326348</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3785816; 3951832</t>
+          <t>3782405; 3961541</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3484703; 3657159</t>
+          <t>3488935; 3657624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2862363; 3516830</t>
+          <t>2868149; 3513583</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,31; 45,53</t>
+          <t>36,17; 45,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,44; 55,7</t>
+          <t>46,3; 55,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,31; 52,63</t>
+          <t>42,65; 52,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,86; 46,04</t>
+          <t>37,45; 46,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,65; 56,37</t>
+          <t>44,72; 56,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,03; 62,16</t>
+          <t>50,16; 62,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,64; 53,65</t>
+          <t>43,17; 54,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,18; 48,21</t>
+          <t>41,29; 49,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,96; 48,21</t>
+          <t>41,29; 48,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,61; 57,26</t>
+          <t>48,99; 56,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,5; 51,7</t>
+          <t>44,46; 51,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,17; 46,28</t>
+          <t>40,56; 46,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,06; 44,34</t>
+          <t>33,95; 44,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,08; 53,37</t>
+          <t>43,2; 53,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,19; 51,4</t>
+          <t>40,81; 51,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,93; 41,18</t>
+          <t>32,04; 40,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,09; 60,56</t>
+          <t>49,96; 59,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,55; 69,75</t>
+          <t>58,48; 69,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,83; 58,46</t>
+          <t>47,75; 58,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,26; 53,68</t>
+          <t>45,26; 54,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,3; 50,88</t>
+          <t>43,15; 50,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,54; 59,12</t>
+          <t>51,66; 59,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,14; 53,52</t>
+          <t>45,9; 53,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,3; 45,74</t>
+          <t>39,41; 45,51</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,77; 48,8</t>
+          <t>40,91; 48,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,67; 57,12</t>
+          <t>48,77; 57,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,59; 54,97</t>
+          <t>46,63; 55,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 46,44</t>
+          <t>40,27; 49,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,69; 64,49</t>
+          <t>48,73; 64,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,71; 71,85</t>
+          <t>59,53; 71,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,45; 68,2</t>
+          <t>52,45; 68,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,28; 60,09</t>
+          <t>48,66; 60,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,25; 51,24</t>
+          <t>44,11; 51,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,23; 60,33</t>
+          <t>53,17; 60,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,06; 56,99</t>
+          <t>49,06; 56,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 48,55</t>
+          <t>43,72; 51,17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,29; 50,81</t>
+          <t>45,18; 50,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,25; 54,49</t>
+          <t>48,11; 54,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,28; 53,19</t>
+          <t>47,44; 53,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,57; 46,43</t>
+          <t>40,26; 46,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,57; 57,55</t>
+          <t>49,69; 57,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,78; 64,4</t>
+          <t>57,31; 64,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,96; 58,73</t>
+          <t>51,85; 58,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,85; 79,04</t>
+          <t>46,43; 52,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,0; 52,55</t>
+          <t>47,91; 52,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,96; 57,57</t>
+          <t>53,04; 57,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,51; 54,81</t>
+          <t>50,09; 54,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,52; 66,78</t>
+          <t>43,79; 48,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,35; 48,57</t>
+          <t>37,28; 48,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,09; 51,19</t>
+          <t>42,35; 51,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,57; 54,36</t>
+          <t>46,3; 54,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,34; 51,22</t>
+          <t>40,6; 50,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,24; 62,79</t>
+          <t>53,66; 62,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,19; 68,01</t>
+          <t>60,62; 68,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,1; 66,82</t>
+          <t>59,17; 66,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,12; 67,28</t>
+          <t>52,21; 58,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,17; 55,69</t>
+          <t>49,51; 55,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,84; 60,42</t>
+          <t>54,74; 60,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,43; 60,07</t>
+          <t>54,53; 59,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,52; 60,84</t>
+          <t>48,24; 53,61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,64; 34,02</t>
+          <t>23,93; 34,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,67; 38,47</t>
+          <t>26,69; 38,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,28; 37,83</t>
+          <t>27,09; 38,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,85; 39,13</t>
+          <t>21,09; 39,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,09; 55,6</t>
+          <t>49,83; 55,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57,36; 63,33</t>
+          <t>57,38; 63,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,84; 53,95</t>
+          <t>47,99; 53,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,68; 54,47</t>
+          <t>46,79; 53,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,76; 50,68</t>
+          <t>45,83; 50,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52,22; 57,75</t>
+          <t>52,34; 57,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,91; 49,78</t>
+          <t>44,24; 49,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,97; 48,33</t>
+          <t>42,23; 49,12</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,54; 44,98</t>
+          <t>41,59; 44,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,46; 50,81</t>
+          <t>47,24; 50,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,37; 49,96</t>
+          <t>46,52; 49,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,17; 41,82</t>
+          <t>39,95; 43,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,46; 55,92</t>
+          <t>52,39; 55,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,15; 63,6</t>
+          <t>60,17; 63,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,21; 56,69</t>
+          <t>53,15; 56,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49,86; 62,79</t>
+          <t>49,27; 52,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,69; 50,03</t>
+          <t>47,56; 50,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54,25; 56,82</t>
+          <t>54,24; 56,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50,44; 52,88</t>
+          <t>50,39; 52,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,45; 50,78</t>
+          <t>45,07; 47,35</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209885</t>
+          <t>228052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>198646</t>
+          <t>220696</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>408532</t>
+          <t>448748</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>172020; 215718</t>
+          <t>171343; 215957</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>198660; 243520</t>
+          <t>202428; 243324</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181553; 225817</t>
+          <t>183005; 226453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>185402; 231597</t>
+          <t>205261; 253758</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>139992; 172871</t>
+          <t>137140; 174010</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>157319; 195472</t>
+          <t>157737; 196063</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>147978; 186190</t>
+          <t>149811; 187568</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>179289; 215093</t>
+          <t>200991; 240810</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>319666; 376275</t>
+          <t>322229; 378112</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>372897; 430433</t>
+          <t>368240; 428078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>345409; 401286</t>
+          <t>345041; 401407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>381295; 439304</t>
+          <t>419765; 481310</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165191</t>
+          <t>175940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>188518</t>
+          <t>208863</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>353708</t>
+          <t>384803</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124975; 162708</t>
+          <t>124567; 163719</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>180398; 223522</t>
+          <t>180918; 224081</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155381; 193907</t>
+          <t>153947; 193742</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144150; 185933</t>
+          <t>154507; 195801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>186274; 225216</t>
+          <t>185790; 220601</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>197902; 235750</t>
+          <t>197674; 236004</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>178043; 217626</t>
+          <t>177779; 218071</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>172879; 205054</t>
+          <t>191226; 228134</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>319936; 375873</t>
+          <t>318786; 374392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>390032; 447447</t>
+          <t>391003; 449292</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>345815; 401136</t>
+          <t>344016; 400799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>327589; 381267</t>
+          <t>356551; 411726</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>189133</t>
+          <t>210048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89742</t>
+          <t>101047</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>278874</t>
+          <t>311096</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>221154; 264703</t>
+          <t>221874; 265470</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>306322; 359513</t>
+          <t>306964; 360663</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>243169; 286879</t>
+          <t>243358; 289418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68038; 308981</t>
+          <t>188727; 231904</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83374; 108198</t>
+          <t>81756; 108445</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>155336; 186897</t>
+          <t>154865; 185773</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85467; 113290</t>
+          <t>87131; 113292</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80101; 99694</t>
+          <t>90719; 113002</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>314274; 363911</t>
+          <t>313253; 364470</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>473510; 536656</t>
+          <t>473007; 535580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>337578; 392133</t>
+          <t>337579; 391934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>134658; 403570</t>
+          <t>286429; 335227</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>441917</t>
+          <t>487706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>579007</t>
+          <t>424846</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1020925</t>
+          <t>912551</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>560805; 629229</t>
+          <t>559505; 630044</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>559184; 631598</t>
+          <t>557624; 631880</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>543590; 611526</t>
+          <t>545361; 613775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407484; 478087</t>
+          <t>453456; 526233</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>354041; 411050</t>
+          <t>354916; 407568</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>435318; 493694</t>
+          <t>439357; 493612</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>429104; 485015</t>
+          <t>428230; 483766</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>466903; 771325</t>
+          <t>398801; 454188</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>937270; 1026198</t>
+          <t>935588; 1023209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1019743; 1108702</t>
+          <t>1021425; 1108549</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>997886; 1082847</t>
+          <t>989548; 1077294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>892954; 1339211</t>
+          <t>869386; 954798</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217614</t>
+          <t>255103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>473535</t>
+          <t>453873</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>691148</t>
+          <t>708977</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>130915; 170269</t>
+          <t>130699; 169124</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>214914; 261379</t>
+          <t>216216; 260911</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>289039; 337445</t>
+          <t>287366; 339338</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194466; 240959</t>
+          <t>228564; 281885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>308518; 357102</t>
+          <t>305185; 356587</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>465943; 517920</t>
+          <t>461652; 518130</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>436271; 493282</t>
+          <t>436844; 491338</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>419337; 562873</t>
+          <t>431228; 479593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>452046; 512003</t>
+          <t>455151; 513794</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>697606; 768597</t>
+          <t>696370; 765360</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739682; 816384</t>
+          <t>740968; 812741</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>634166; 795200</t>
+          <t>670066; 744640</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64403</t>
+          <t>68526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>383677</t>
+          <t>421802</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>448080</t>
+          <t>490329</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70506; 101439</t>
+          <t>71348; 102678</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71178; 102671</t>
+          <t>71229; 102083</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78328; 108623</t>
+          <t>77788; 109851</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45343; 94102</t>
+          <t>50022; 92621</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>625518; 694322</t>
+          <t>622288; 692792</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>636342; 702602</t>
+          <t>636596; 700106</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>517638; 583792</t>
+          <t>519251; 582975</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>358848; 409917</t>
+          <t>390805; 448531</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>707950; 783959</t>
+          <t>708939; 787161</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>718721; 794843</t>
+          <t>720361; 793129</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>601245; 681603</t>
+          <t>605659; 679560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>406841; 480013</t>
+          <t>452919; 526737</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1288143</t>
+          <t>1425375</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1913125</t>
+          <t>1831128</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3201268</t>
+          <t>3256503</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1358481; 1471031</t>
+          <t>1360195; 1471211</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1624206; 1738806</t>
+          <t>1616654; 1737584</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1570094; 1691389</t>
+          <t>1574892; 1688535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>980323; 1405243</t>
+          <t>1368436; 1494974</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1772265; 1889033</t>
+          <t>1769705; 1887370</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2135351; 2257824</t>
+          <t>2136163; 2258275</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1879204; 2002031</t>
+          <t>1876969; 1998196</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1774767; 2234950</t>
+          <t>1781540; 1884849</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3170890; 3326348</t>
+          <t>3162210; 3333735</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3782405; 3961541</t>
+          <t>3781642; 3955352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3488935; 3657624</t>
+          <t>3485543; 3662135</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2868149; 3513583</t>
+          <t>3173568; 3333723</t>
         </is>
       </c>
     </row>
